--- a/Topologija/IPv4 shema.xlsx
+++ b/Topologija/IPv4 shema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zverm\Documents\Cisco omrežje\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\developer\Downloads\CISCO-omrezje-master\Topologija\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED83772F-109E-4AA7-995A-F8F13791E3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69DBE822-7179-4869-B223-6CF5F5D1D2D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{47F164FE-B6BA-404D-9A6D-E8F24F315E06}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{47F164FE-B6BA-404D-9A6D-E8F24F315E06}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -75,15 +75,6 @@
     <t>192.168.100.1/24</t>
   </si>
   <si>
-    <t>192.168.200.1/24</t>
-  </si>
-  <si>
-    <t>192.168.201.2/24</t>
-  </si>
-  <si>
-    <t>192.168.200.2/24</t>
-  </si>
-  <si>
     <t>192.168.2.1/24</t>
   </si>
   <si>
@@ -93,9 +84,6 @@
     <t>192.168.102.2/24</t>
   </si>
   <si>
-    <t>192.168.201.1/24</t>
-  </si>
-  <si>
     <t>192.168.1.1/24</t>
   </si>
   <si>
@@ -117,12 +105,6 @@
     <t>192.168.4.2/24</t>
   </si>
   <si>
-    <t>192.168.200.0/24</t>
-  </si>
-  <si>
-    <t>192.168.201.0/24</t>
-  </si>
-  <si>
     <t>192.168.100.0/24</t>
   </si>
   <si>
@@ -169,6 +151,24 @@
   </si>
   <si>
     <t>Devices</t>
+  </si>
+  <si>
+    <t>192.168.200.0/30</t>
+  </si>
+  <si>
+    <t>192.168.201.0/30</t>
+  </si>
+  <si>
+    <t>192.168.200.1/30</t>
+  </si>
+  <si>
+    <t>192.168.200.2/30</t>
+  </si>
+  <si>
+    <t>192.168.201.1/30</t>
+  </si>
+  <si>
+    <t>192.168.201.2/30</t>
   </si>
 </sst>
 </file>
@@ -439,37 +439,37 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Navadno" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -485,9 +485,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Officeova tema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Pisarna">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -525,7 +525,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Pisarna">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -631,7 +631,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Pisarna">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -773,7 +773,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -822,10 +822,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -835,10 +835,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -848,16 +848,16 @@
         <v>7</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -865,16 +865,16 @@
         <v>8</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -882,115 +882,115 @@
         <v>9</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="15" t="s">
-        <v>21</v>
-      </c>
       <c r="E7" s="15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
+      <c r="A9" s="24"/>
       <c r="B9" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="27"/>
+      <c r="B11" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24"/>
-      <c r="B11" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="23" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
-        <v>42</v>
-      </c>
       <c r="B13" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="27"/>
+      <c r="B14" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24"/>
-      <c r="B14" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="23" t="s">
-        <v>43</v>
-      </c>
       <c r="B15" s="22" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="26"/>
       <c r="B16" s="22" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="26"/>
       <c r="B17" s="22" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24"/>
+      <c r="A18" s="27"/>
       <c r="B18" s="22" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
